--- a/dataset_t6_grouped/results2/G5/G5_T1791L_W0035F0003T0006Z000C1N38_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T1791L_W0035F0003T0006Z000C1N38_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>97.83858262333139</v>
+        <v>15.89876967629135</v>
       </c>
       <c r="D2" t="n">
-        <v>96.30187813836694</v>
+        <v>15.64905519748463</v>
       </c>
       <c r="E2" t="n">
-        <v>21.98091342237604</v>
+        <v>3.571898431136106</v>
       </c>
       <c r="F2" t="n">
-        <v>21.38429629289573</v>
+        <v>3.474948147595557</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>80.06876239962259</v>
+        <v>13.01117388993867</v>
       </c>
       <c r="D3" t="n">
-        <v>78.50295072818356</v>
+        <v>12.75672949332983</v>
       </c>
       <c r="E3" t="n">
-        <v>21.98091342237604</v>
+        <v>3.571898431136106</v>
       </c>
       <c r="F3" t="n">
-        <v>21.38429629289573</v>
+        <v>3.474948147595557</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>94.95133289850358</v>
+        <v>15.42959159600683</v>
       </c>
       <c r="D4" t="n">
-        <v>93.69055531557692</v>
+        <v>15.22471523878125</v>
       </c>
       <c r="E4" t="n">
-        <v>21.98091342237604</v>
+        <v>3.571898431136106</v>
       </c>
       <c r="F4" t="n">
-        <v>21.38429629289573</v>
+        <v>3.474948147595557</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>81.89832983320069</v>
+        <v>13.30847859789511</v>
       </c>
       <c r="D5" t="n">
-        <v>80.19146657631207</v>
+        <v>13.03111331865071</v>
       </c>
       <c r="E5" t="n">
-        <v>21.98091342237604</v>
+        <v>3.571898431136106</v>
       </c>
       <c r="F5" t="n">
-        <v>21.38429629289573</v>
+        <v>3.474948147595557</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>63.17181247985324</v>
+        <v>10.26541952797615</v>
       </c>
       <c r="D6" t="n">
-        <v>61.09857739450032</v>
+        <v>9.928518826606304</v>
       </c>
       <c r="E6" t="n">
-        <v>21.98091342237604</v>
+        <v>3.571898431136106</v>
       </c>
       <c r="F6" t="n">
-        <v>21.38429629289573</v>
+        <v>3.474948147595557</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>68.13320175389383</v>
+        <v>11.07164528500775</v>
       </c>
       <c r="D7" t="n">
-        <v>66.51734670887991</v>
+        <v>10.80906884019299</v>
       </c>
       <c r="E7" t="n">
-        <v>21.98091342237604</v>
+        <v>3.571898431136106</v>
       </c>
       <c r="F7" t="n">
-        <v>21.38429629289573</v>
+        <v>3.474948147595557</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>71.46930662191896</v>
+        <v>11.61376232606183</v>
       </c>
       <c r="D8" t="n">
-        <v>69.74196831110146</v>
+        <v>11.33306985055399</v>
       </c>
       <c r="E8" t="n">
-        <v>21.98091342237604</v>
+        <v>3.571898431136106</v>
       </c>
       <c r="F8" t="n">
-        <v>21.38429629289573</v>
+        <v>3.474948147595557</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>60.73340438640181</v>
+        <v>9.869178212790294</v>
       </c>
       <c r="D9" t="n">
-        <v>58.77772710856952</v>
+        <v>9.551380655142548</v>
       </c>
       <c r="E9" t="n">
-        <v>21.98091342237604</v>
+        <v>3.571898431136106</v>
       </c>
       <c r="F9" t="n">
-        <v>21.38429629289573</v>
+        <v>3.474948147595557</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>56.02853844952508</v>
+        <v>9.104637498047826</v>
       </c>
       <c r="D10" t="n">
-        <v>53.97418403854936</v>
+        <v>8.770804906264271</v>
       </c>
       <c r="E10" t="n">
-        <v>21.98091342237604</v>
+        <v>3.571898431136106</v>
       </c>
       <c r="F10" t="n">
-        <v>21.38429629289573</v>
+        <v>3.474948147595557</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>58.65613166480522</v>
+        <v>9.531621395530848</v>
       </c>
       <c r="D11" t="n">
-        <v>56.84826159505512</v>
+        <v>9.237842509196458</v>
       </c>
       <c r="E11" t="n">
-        <v>21.98091342237604</v>
+        <v>3.571898431136106</v>
       </c>
       <c r="F11" t="n">
-        <v>21.38429629289573</v>
+        <v>3.474948147595557</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>86.84817180533365</v>
+        <v>14.11282791836672</v>
       </c>
       <c r="D12" t="n">
-        <v>85.69338281643752</v>
+        <v>13.9251747076711</v>
       </c>
       <c r="E12" t="n">
-        <v>21.98091342237604</v>
+        <v>3.571898431136106</v>
       </c>
       <c r="F12" t="n">
-        <v>21.38429629289573</v>
+        <v>3.474948147595557</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>59.35942153205607</v>
+        <v>9.645905998959112</v>
       </c>
       <c r="D13" t="n">
-        <v>57.68760923959363</v>
+        <v>9.374236501433964</v>
       </c>
       <c r="E13" t="n">
-        <v>21.98091342237604</v>
+        <v>3.571898431136106</v>
       </c>
       <c r="F13" t="n">
-        <v>21.38429629289573</v>
+        <v>3.474948147595557</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>52.89680243643141</v>
+        <v>8.595730395920105</v>
       </c>
       <c r="D14" t="n">
-        <v>50.89008190286715</v>
+        <v>8.269638309215912</v>
       </c>
       <c r="E14" t="n">
-        <v>21.98091342237604</v>
+        <v>3.571898431136106</v>
       </c>
       <c r="F14" t="n">
-        <v>21.38429629289573</v>
+        <v>3.474948147595557</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>50.50340486743882</v>
+        <v>8.206803290958808</v>
       </c>
       <c r="D15" t="n">
-        <v>48.49711038707936</v>
+        <v>7.880780437900397</v>
       </c>
       <c r="E15" t="n">
-        <v>21.98091342237604</v>
+        <v>3.571898431136106</v>
       </c>
       <c r="F15" t="n">
-        <v>21.38429629289573</v>
+        <v>3.474948147595557</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>83.73943625715324</v>
+        <v>13.6076583917874</v>
       </c>
       <c r="D16" t="n">
-        <v>82.3338889482233</v>
+        <v>13.37925695408629</v>
       </c>
       <c r="E16" t="n">
-        <v>21.98091342237604</v>
+        <v>3.571898431136106</v>
       </c>
       <c r="F16" t="n">
-        <v>21.38429629289573</v>
+        <v>3.474948147595557</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>48.96646647471258</v>
+        <v>7.957050802140794</v>
       </c>
       <c r="D17" t="n">
-        <v>47.24639768133105</v>
+        <v>7.677539623216297</v>
       </c>
       <c r="E17" t="n">
-        <v>21.98091342237604</v>
+        <v>3.571898431136106</v>
       </c>
       <c r="F17" t="n">
-        <v>21.38429629289573</v>
+        <v>3.474948147595557</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -992,16 +992,16 @@
         <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>75.04530346418665</v>
+        <v>12.19486181293033</v>
       </c>
       <c r="D18" t="n">
-        <v>74.04850468664664</v>
+        <v>12.03288201158008</v>
       </c>
       <c r="E18" t="n">
-        <v>21.98091342237604</v>
+        <v>3.571898431136106</v>
       </c>
       <c r="F18" t="n">
-        <v>21.38429629289573</v>
+        <v>3.474948147595557</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1024,16 +1024,16 @@
         <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>50.47718103950702</v>
+        <v>8.202541918919891</v>
       </c>
       <c r="D19" t="n">
-        <v>48.70161016201968</v>
+        <v>7.914011651328198</v>
       </c>
       <c r="E19" t="n">
-        <v>21.98091342237604</v>
+        <v>3.571898431136106</v>
       </c>
       <c r="F19" t="n">
-        <v>21.38429629289573</v>
+        <v>3.474948147595557</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1056,16 +1056,16 @@
         <v>19</v>
       </c>
       <c r="C20" t="n">
-        <v>59.1589192821377</v>
+        <v>9.613324383347377</v>
       </c>
       <c r="D20" t="n">
-        <v>57.65566616663691</v>
+        <v>9.369045752078497</v>
       </c>
       <c r="E20" t="n">
-        <v>21.98091342237604</v>
+        <v>3.571898431136106</v>
       </c>
       <c r="F20" t="n">
-        <v>21.38429629289573</v>
+        <v>3.474948147595557</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1088,16 +1088,16 @@
         <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>78.71659078226507</v>
+        <v>12.79144600211808</v>
       </c>
       <c r="D21" t="n">
-        <v>77.91732985025003</v>
+        <v>12.66156610066563</v>
       </c>
       <c r="E21" t="n">
-        <v>21.98091342237604</v>
+        <v>3.571898431136106</v>
       </c>
       <c r="F21" t="n">
-        <v>21.38429629289573</v>
+        <v>3.474948147595557</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1120,16 +1120,16 @@
         <v>21</v>
       </c>
       <c r="C22" t="n">
-        <v>35.86729153913658</v>
+        <v>5.828434875109695</v>
       </c>
       <c r="D22" t="n">
-        <v>33.80516630963718</v>
+        <v>5.493339525316042</v>
       </c>
       <c r="E22" t="n">
-        <v>21.98091342237604</v>
+        <v>3.571898431136106</v>
       </c>
       <c r="F22" t="n">
-        <v>21.38429629289573</v>
+        <v>3.474948147595557</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1152,16 +1152,16 @@
         <v>22</v>
       </c>
       <c r="C23" t="n">
-        <v>55.36945421736647</v>
+        <v>8.997536310322051</v>
       </c>
       <c r="D23" t="n">
-        <v>54.30123969212461</v>
+        <v>8.823951449970249</v>
       </c>
       <c r="E23" t="n">
-        <v>21.98091342237604</v>
+        <v>3.571898431136106</v>
       </c>
       <c r="F23" t="n">
-        <v>21.38429629289573</v>
+        <v>3.474948147595557</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1184,16 +1184,16 @@
         <v>23</v>
       </c>
       <c r="C24" t="n">
-        <v>36.01304715448559</v>
+        <v>5.852120162603908</v>
       </c>
       <c r="D24" t="n">
-        <v>33.95071697297575</v>
+        <v>5.516991508108561</v>
       </c>
       <c r="E24" t="n">
-        <v>21.98091342237604</v>
+        <v>3.571898431136106</v>
       </c>
       <c r="F24" t="n">
-        <v>21.38429629289573</v>
+        <v>3.474948147595557</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -1216,16 +1216,16 @@
         <v>24</v>
       </c>
       <c r="C25" t="n">
-        <v>73.18558069907297</v>
+        <v>11.89265686359936</v>
       </c>
       <c r="D25" t="n">
-        <v>65</v>
+        <v>10.5625</v>
       </c>
       <c r="E25" t="n">
-        <v>21.98091342237604</v>
+        <v>3.571898431136106</v>
       </c>
       <c r="F25" t="n">
-        <v>21.38429629289573</v>
+        <v>3.474948147595557</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -1248,16 +1248,16 @@
         <v>25</v>
       </c>
       <c r="C26" t="n">
-        <v>39.53446139985529</v>
+        <v>6.424349977476485</v>
       </c>
       <c r="D26" t="n">
-        <v>37.71066089350387</v>
+        <v>6.127982395194379</v>
       </c>
       <c r="E26" t="n">
-        <v>21.98091342237604</v>
+        <v>3.571898431136106</v>
       </c>
       <c r="F26" t="n">
-        <v>21.38429629289573</v>
+        <v>3.474948147595557</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -1280,16 +1280,16 @@
         <v>26</v>
       </c>
       <c r="C27" t="n">
-        <v>54.38000199296947</v>
+        <v>8.836750323857538</v>
       </c>
       <c r="D27" t="n">
-        <v>53.07178253186547</v>
+        <v>8.624164661428139</v>
       </c>
       <c r="E27" t="n">
-        <v>21.98091342237604</v>
+        <v>3.571898431136106</v>
       </c>
       <c r="F27" t="n">
-        <v>21.38429629289573</v>
+        <v>3.474948147595557</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -1312,16 +1312,16 @@
         <v>27</v>
       </c>
       <c r="C28" t="n">
-        <v>64.42398712863306</v>
+        <v>10.46889790840287</v>
       </c>
       <c r="D28" t="n">
-        <v>63.66593451982965</v>
+        <v>10.34571435947232</v>
       </c>
       <c r="E28" t="n">
-        <v>21.98091342237604</v>
+        <v>3.571898431136106</v>
       </c>
       <c r="F28" t="n">
-        <v>21.38429629289573</v>
+        <v>3.474948147595557</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -1344,16 +1344,16 @@
         <v>28</v>
       </c>
       <c r="C29" t="n">
-        <v>75.53042410635339</v>
+        <v>12.27369391728243</v>
       </c>
       <c r="D29" t="n">
-        <v>74.91997356068433</v>
+        <v>12.1744957036112</v>
       </c>
       <c r="E29" t="n">
-        <v>21.98091342237604</v>
+        <v>3.571898431136106</v>
       </c>
       <c r="F29" t="n">
-        <v>21.38429629289573</v>
+        <v>3.474948147595557</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -1376,16 +1376,16 @@
         <v>29</v>
       </c>
       <c r="C30" t="n">
-        <v>31.89595048746046</v>
+        <v>5.183091954212324</v>
       </c>
       <c r="D30" t="n">
-        <v>30.04886373737204</v>
+        <v>4.882940357322957</v>
       </c>
       <c r="E30" t="n">
-        <v>21.98091342237604</v>
+        <v>3.571898431136106</v>
       </c>
       <c r="F30" t="n">
-        <v>21.38429629289573</v>
+        <v>3.474948147595557</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -1408,16 +1408,16 @@
         <v>30</v>
       </c>
       <c r="C31" t="n">
-        <v>82.16226746445706</v>
+        <v>13.35136846297427</v>
       </c>
       <c r="D31" t="n">
-        <v>62.75968274121354</v>
+        <v>10.1984484454472</v>
       </c>
       <c r="E31" t="n">
-        <v>21.98091342237604</v>
+        <v>3.571898431136106</v>
       </c>
       <c r="F31" t="n">
-        <v>21.38429629289573</v>
+        <v>3.474948147595557</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -1440,16 +1440,16 @@
         <v>31</v>
       </c>
       <c r="C32" t="n">
-        <v>35.81871688724596</v>
+        <v>5.820541494177468</v>
       </c>
       <c r="D32" t="n">
-        <v>34.831980057456</v>
+        <v>5.660196759336601</v>
       </c>
       <c r="E32" t="n">
-        <v>21.98091342237604</v>
+        <v>3.571898431136106</v>
       </c>
       <c r="F32" t="n">
-        <v>21.38429629289573</v>
+        <v>3.474948147595557</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -1472,16 +1472,16 @@
         <v>32</v>
       </c>
       <c r="C33" t="n">
-        <v>44.33772103970933</v>
+        <v>7.204879668952766</v>
       </c>
       <c r="D33" t="n">
-        <v>43.30216677807176</v>
+        <v>7.036602101436662</v>
       </c>
       <c r="E33" t="n">
-        <v>21.98091342237604</v>
+        <v>3.571898431136106</v>
       </c>
       <c r="F33" t="n">
-        <v>21.38429629289573</v>
+        <v>3.474948147595557</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -1504,16 +1504,16 @@
         <v>33</v>
       </c>
       <c r="C34" t="n">
-        <v>67.60535875644882</v>
+        <v>10.98587079792293</v>
       </c>
       <c r="D34" t="n">
-        <v>67.3751993522186</v>
+        <v>10.94846989473552</v>
       </c>
       <c r="E34" t="n">
-        <v>21.98091342237604</v>
+        <v>3.571898431136106</v>
       </c>
       <c r="F34" t="n">
-        <v>21.38429629289573</v>
+        <v>3.474948147595557</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
@@ -1536,16 +1536,16 @@
         <v>34</v>
       </c>
       <c r="C35" t="n">
-        <v>29.33628702604428</v>
+        <v>4.767146641732196</v>
       </c>
       <c r="D35" t="n">
-        <v>28.04999625651138</v>
+        <v>4.5581243916831</v>
       </c>
       <c r="E35" t="n">
-        <v>21.98091342237604</v>
+        <v>3.571898431136106</v>
       </c>
       <c r="F35" t="n">
-        <v>21.38429629289573</v>
+        <v>3.474948147595557</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
@@ -1568,16 +1568,16 @@
         <v>35</v>
       </c>
       <c r="C36" t="n">
-        <v>37.67238372210065</v>
+        <v>6.121762354841356</v>
       </c>
       <c r="D36" t="n">
-        <v>37.13591114899248</v>
+        <v>6.034585561711277</v>
       </c>
       <c r="E36" t="n">
-        <v>21.98091342237604</v>
+        <v>3.571898431136106</v>
       </c>
       <c r="F36" t="n">
-        <v>21.38429629289573</v>
+        <v>3.474948147595557</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
@@ -1600,16 +1600,16 @@
         <v>36</v>
       </c>
       <c r="C37" t="n">
-        <v>48.05465845411093</v>
+        <v>7.808881998793026</v>
       </c>
       <c r="D37" t="n">
-        <v>47.65783456715924</v>
+        <v>7.744398117163377</v>
       </c>
       <c r="E37" t="n">
-        <v>21.98091342237604</v>
+        <v>3.571898431136106</v>
       </c>
       <c r="F37" t="n">
-        <v>21.38429629289573</v>
+        <v>3.474948147595557</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
@@ -1632,16 +1632,16 @@
         <v>37</v>
       </c>
       <c r="C38" t="n">
-        <v>34.23930262377873</v>
+        <v>5.563886676364043</v>
       </c>
       <c r="D38" t="n">
-        <v>33.46662363085238</v>
+        <v>5.438326340013512</v>
       </c>
       <c r="E38" t="n">
-        <v>21.98091342237604</v>
+        <v>3.571898431136106</v>
       </c>
       <c r="F38" t="n">
-        <v>21.38429629289573</v>
+        <v>3.474948147595557</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
@@ -1664,16 +1664,16 @@
         <v>38</v>
       </c>
       <c r="C39" t="n">
-        <v>72.69969107555137</v>
+        <v>11.8136997997771</v>
       </c>
       <c r="D39" t="n">
-        <v>48.47803626385871</v>
+        <v>7.877680892877041</v>
       </c>
       <c r="E39" t="n">
-        <v>21.98091342237604</v>
+        <v>3.571898431136106</v>
       </c>
       <c r="F39" t="n">
-        <v>21.38429629289573</v>
+        <v>3.474948147595557</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
@@ -1696,16 +1696,16 @@
         <v>39</v>
       </c>
       <c r="C40" t="n">
-        <v>17.34316533857386</v>
+        <v>2.818264367518252</v>
       </c>
       <c r="D40" t="n">
-        <v>15.62473514111114</v>
+        <v>2.53901946043056</v>
       </c>
       <c r="E40" t="n">
-        <v>21.98091342237604</v>
+        <v>3.571898431136106</v>
       </c>
       <c r="F40" t="n">
-        <v>21.38429629289573</v>
+        <v>3.474948147595557</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
@@ -1728,16 +1728,16 @@
         <v>40</v>
       </c>
       <c r="C41" t="n">
-        <v>19.66313284315738</v>
+        <v>3.195259087013075</v>
       </c>
       <c r="D41" t="n">
-        <v>18.42741947982707</v>
+        <v>2.994455665471899</v>
       </c>
       <c r="E41" t="n">
-        <v>21.98091342237604</v>
+        <v>3.571898431136106</v>
       </c>
       <c r="F41" t="n">
-        <v>21.38429629289573</v>
+        <v>3.474948147595557</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
@@ -1760,16 +1760,16 @@
         <v>41</v>
       </c>
       <c r="C42" t="n">
-        <v>34.43217242617833</v>
+        <v>5.595228019253979</v>
       </c>
       <c r="D42" t="n">
-        <v>34.32472830387712</v>
+        <v>5.577768349380032</v>
       </c>
       <c r="E42" t="n">
-        <v>21.98091342237604</v>
+        <v>3.571898431136106</v>
       </c>
       <c r="F42" t="n">
-        <v>21.38429629289573</v>
+        <v>3.474948147595557</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
@@ -1792,16 +1792,16 @@
         <v>42</v>
       </c>
       <c r="C43" t="n">
-        <v>54.51984626994465</v>
+        <v>8.859475018866005</v>
       </c>
       <c r="D43" t="n">
-        <v>54.60820333458344</v>
+        <v>8.873833041869808</v>
       </c>
       <c r="E43" t="n">
-        <v>21.98091342237604</v>
+        <v>3.571898431136106</v>
       </c>
       <c r="F43" t="n">
-        <v>21.38429629289573</v>
+        <v>3.474948147595557</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
@@ -1824,16 +1824,16 @@
         <v>43</v>
       </c>
       <c r="C44" t="n">
-        <v>23.23631721773397</v>
+        <v>3.775901547881769</v>
       </c>
       <c r="D44" t="n">
-        <v>22.66505033467432</v>
+        <v>3.683070679384576</v>
       </c>
       <c r="E44" t="n">
-        <v>21.98091342237604</v>
+        <v>3.571898431136106</v>
       </c>
       <c r="F44" t="n">
-        <v>21.38429629289573</v>
+        <v>3.474948147595557</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
@@ -1856,16 +1856,16 @@
         <v>44</v>
       </c>
       <c r="C45" t="n">
-        <v>7.157309161826042</v>
+        <v>1.163062738796732</v>
       </c>
       <c r="D45" t="n">
-        <v>7.158499423842694</v>
+        <v>1.163256156374438</v>
       </c>
       <c r="E45" t="n">
-        <v>21.98091342237604</v>
+        <v>3.571898431136106</v>
       </c>
       <c r="F45" t="n">
-        <v>21.38429629289573</v>
+        <v>3.474948147595557</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
@@ -1888,16 +1888,16 @@
         <v>45</v>
       </c>
       <c r="C46" t="n">
-        <v>45.19604141161687</v>
+        <v>7.344356729387742</v>
       </c>
       <c r="D46" t="n">
-        <v>30.08506458545687</v>
+        <v>4.888822995136742</v>
       </c>
       <c r="E46" t="n">
-        <v>21.98091342237604</v>
+        <v>3.571898431136106</v>
       </c>
       <c r="F46" t="n">
-        <v>21.38429629289573</v>
+        <v>3.474948147595557</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
@@ -1920,16 +1920,16 @@
         <v>46</v>
       </c>
       <c r="C47" t="n">
-        <v>34.69192279902992</v>
+        <v>5.637437454842362</v>
       </c>
       <c r="D47" t="n">
-        <v>33.76758800980609</v>
+        <v>5.48723305159349</v>
       </c>
       <c r="E47" t="n">
-        <v>21.98091342237604</v>
+        <v>3.571898431136106</v>
       </c>
       <c r="F47" t="n">
-        <v>21.38429629289573</v>
+        <v>3.474948147595557</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
@@ -1952,16 +1952,16 @@
         <v>47</v>
       </c>
       <c r="C48" t="n">
-        <v>4.728071664099359</v>
+        <v>0.7683116454161459</v>
       </c>
       <c r="D48" t="n">
-        <v>6.095404882689511</v>
+        <v>0.9905032934370456</v>
       </c>
       <c r="E48" t="n">
-        <v>21.98091342237604</v>
+        <v>3.571898431136106</v>
       </c>
       <c r="F48" t="n">
-        <v>21.38429629289573</v>
+        <v>3.474948147595557</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
@@ -1984,16 +1984,16 @@
         <v>48</v>
       </c>
       <c r="C49" t="n">
-        <v>28.69744261533738</v>
+        <v>4.663334424992325</v>
       </c>
       <c r="D49" t="n">
-        <v>29.18730947322744</v>
+        <v>4.742937789399458</v>
       </c>
       <c r="E49" t="n">
-        <v>21.98091342237604</v>
+        <v>3.571898431136106</v>
       </c>
       <c r="F49" t="n">
-        <v>21.38429629289573</v>
+        <v>3.474948147595557</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
@@ -2016,16 +2016,16 @@
         <v>49</v>
       </c>
       <c r="C50" t="n">
-        <v>47.95566024603947</v>
+        <v>7.792794789981414</v>
       </c>
       <c r="D50" t="n">
-        <v>47.85102513364172</v>
+        <v>7.77579158421678</v>
       </c>
       <c r="E50" t="n">
-        <v>21.98091342237604</v>
+        <v>3.571898431136106</v>
       </c>
       <c r="F50" t="n">
-        <v>21.38429629289573</v>
+        <v>3.474948147595557</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
@@ -2048,16 +2048,16 @@
         <v>50</v>
       </c>
       <c r="C51" t="n">
-        <v>16.06168041522136</v>
+        <v>2.610023067473471</v>
       </c>
       <c r="D51" t="n">
-        <v>16.85532878762999</v>
+        <v>2.738990927989874</v>
       </c>
       <c r="E51" t="n">
-        <v>21.98091342237604</v>
+        <v>3.571898431136106</v>
       </c>
       <c r="F51" t="n">
-        <v>21.38429629289573</v>
+        <v>3.474948147595557</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
@@ -2080,16 +2080,16 @@
         <v>51</v>
       </c>
       <c r="C52" t="n">
-        <v>63.02320796892563</v>
+        <v>10.24127129495042</v>
       </c>
       <c r="D52" t="n">
-        <v>57.65266910961902</v>
+        <v>9.36855873031309</v>
       </c>
       <c r="E52" t="n">
-        <v>21.98091342237604</v>
+        <v>3.571898431136106</v>
       </c>
       <c r="F52" t="n">
-        <v>21.38429629289573</v>
+        <v>3.474948147595557</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
@@ -2112,16 +2112,16 @@
         <v>52</v>
       </c>
       <c r="C53" t="n">
-        <v>70.58825201533833</v>
+        <v>11.47059095249248</v>
       </c>
       <c r="D53" t="n">
-        <v>30.11852735374304</v>
+        <v>4.894260694983245</v>
       </c>
       <c r="E53" t="n">
-        <v>21.98091342237604</v>
+        <v>3.571898431136106</v>
       </c>
       <c r="F53" t="n">
-        <v>21.38429629289573</v>
+        <v>3.474948147595557</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
@@ -2144,16 +2144,16 @@
         <v>53</v>
       </c>
       <c r="C54" t="n">
-        <v>44.41949278438211</v>
+        <v>7.218167577462093</v>
       </c>
       <c r="D54" t="n">
-        <v>40.48089750092954</v>
+        <v>6.57814584390105</v>
       </c>
       <c r="E54" t="n">
-        <v>21.98091342237604</v>
+        <v>3.571898431136106</v>
       </c>
       <c r="F54" t="n">
-        <v>21.38429629289573</v>
+        <v>3.474948147595557</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
@@ -2176,16 +2176,16 @@
         <v>54</v>
       </c>
       <c r="C55" t="n">
-        <v>22.84642120998504</v>
+        <v>3.712543446622569</v>
       </c>
       <c r="D55" t="n">
-        <v>23.68856593657095</v>
+        <v>3.849391964692779</v>
       </c>
       <c r="E55" t="n">
-        <v>21.98091342237604</v>
+        <v>3.571898431136106</v>
       </c>
       <c r="F55" t="n">
-        <v>21.38429629289573</v>
+        <v>3.474948147595557</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
@@ -2208,16 +2208,16 @@
         <v>55</v>
       </c>
       <c r="C56" t="n">
-        <v>54.76321197022257</v>
+        <v>8.899021945161168</v>
       </c>
       <c r="D56" t="n">
-        <v>18.74166481399131</v>
+        <v>3.045520532273589</v>
       </c>
       <c r="E56" t="n">
-        <v>21.98091342237604</v>
+        <v>3.571898431136106</v>
       </c>
       <c r="F56" t="n">
-        <v>21.38429629289573</v>
+        <v>3.474948147595557</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
@@ -2240,16 +2240,16 @@
         <v>56</v>
       </c>
       <c r="C57" t="n">
-        <v>69.19406510133309</v>
+        <v>11.24403557896663</v>
       </c>
       <c r="D57" t="n">
-        <v>22.67156809750927</v>
+        <v>3.684129815845256</v>
       </c>
       <c r="E57" t="n">
-        <v>21.98091342237604</v>
+        <v>3.571898431136106</v>
       </c>
       <c r="F57" t="n">
-        <v>21.38429629289573</v>
+        <v>3.474948147595557</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
@@ -2272,16 +2272,16 @@
         <v>57</v>
       </c>
       <c r="C58" t="n">
-        <v>67.93190170187383</v>
+        <v>11.0389340265545</v>
       </c>
       <c r="D58" t="n">
-        <v>58.60525462361124</v>
+        <v>9.523353876336827</v>
       </c>
       <c r="E58" t="n">
-        <v>21.98091342237604</v>
+        <v>3.571898431136106</v>
       </c>
       <c r="F58" t="n">
-        <v>21.38429629289573</v>
+        <v>3.474948147595557</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
@@ -2304,16 +2304,16 @@
         <v>58</v>
       </c>
       <c r="C59" t="n">
-        <v>13.28558281287722</v>
+        <v>2.158907207092549</v>
       </c>
       <c r="D59" t="n">
-        <v>15.25110387460689</v>
+        <v>2.47830437962362</v>
       </c>
       <c r="E59" t="n">
-        <v>21.98091342237604</v>
+        <v>3.571898431136106</v>
       </c>
       <c r="F59" t="n">
-        <v>21.38429629289573</v>
+        <v>3.474948147595557</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
@@ -2336,16 +2336,16 @@
         <v>59</v>
       </c>
       <c r="C60" t="n">
-        <v>60.92972514243012</v>
+        <v>9.901080335644895</v>
       </c>
       <c r="D60" t="n">
-        <v>15.69235482647522</v>
+        <v>2.550007659302223</v>
       </c>
       <c r="E60" t="n">
-        <v>21.98091342237604</v>
+        <v>3.571898431136106</v>
       </c>
       <c r="F60" t="n">
-        <v>21.38429629289573</v>
+        <v>3.474948147595557</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
@@ -2368,16 +2368,16 @@
         <v>60</v>
       </c>
       <c r="C61" t="n">
-        <v>33.34411501881709</v>
+        <v>5.418418690557776</v>
       </c>
       <c r="D61" t="n">
-        <v>25.98175397140439</v>
+        <v>4.222035020353213</v>
       </c>
       <c r="E61" t="n">
-        <v>21.98091342237604</v>
+        <v>3.571898431136106</v>
       </c>
       <c r="F61" t="n">
-        <v>21.38429629289573</v>
+        <v>3.474948147595557</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
@@ -2400,16 +2400,16 @@
         <v>61</v>
       </c>
       <c r="C62" t="n">
-        <v>40.8300250935203</v>
+        <v>6.634879077697049</v>
       </c>
       <c r="D62" t="n">
-        <v>29.52890945702858</v>
+        <v>4.798447786767144</v>
       </c>
       <c r="E62" t="n">
-        <v>21.98091342237604</v>
+        <v>3.571898431136106</v>
       </c>
       <c r="F62" t="n">
-        <v>21.38429629289573</v>
+        <v>3.474948147595557</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
@@ -2432,16 +2432,16 @@
         <v>62</v>
       </c>
       <c r="C63" t="n">
-        <v>60.16668961313491</v>
+        <v>9.777087062134422</v>
       </c>
       <c r="D63" t="n">
-        <v>49.69586253527694</v>
+        <v>8.075577661982503</v>
       </c>
       <c r="E63" t="n">
-        <v>21.98091342237604</v>
+        <v>3.571898431136106</v>
       </c>
       <c r="F63" t="n">
-        <v>21.38429629289573</v>
+        <v>3.474948147595557</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
@@ -2464,16 +2464,16 @@
         <v>63</v>
       </c>
       <c r="C64" t="n">
-        <v>78.21856954549251</v>
+        <v>12.71051755114253</v>
       </c>
       <c r="D64" t="n">
-        <v>26.92582403567252</v>
+        <v>4.375446405796785</v>
       </c>
       <c r="E64" t="n">
-        <v>21.98091342237604</v>
+        <v>3.571898431136106</v>
       </c>
       <c r="F64" t="n">
-        <v>21.38429629289573</v>
+        <v>3.474948147595557</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
@@ -2496,16 +2496,16 @@
         <v>64</v>
       </c>
       <c r="C65" t="n">
-        <v>20.95239002859772</v>
+        <v>3.404763379647129</v>
       </c>
       <c r="D65" t="n">
-        <v>10.51755092135524</v>
+        <v>1.709102024720226</v>
       </c>
       <c r="E65" t="n">
-        <v>21.98091342237604</v>
+        <v>3.571898431136106</v>
       </c>
       <c r="F65" t="n">
-        <v>21.38429629289573</v>
+        <v>3.474948147595557</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
@@ -2528,16 +2528,16 @@
         <v>65</v>
       </c>
       <c r="C66" t="n">
-        <v>63.57322193533594</v>
+        <v>10.33064856449209</v>
       </c>
       <c r="D66" t="n">
-        <v>10</v>
+        <v>1.625</v>
       </c>
       <c r="E66" t="n">
-        <v>21.98091342237604</v>
+        <v>3.571898431136106</v>
       </c>
       <c r="F66" t="n">
-        <v>21.38429629289573</v>
+        <v>3.474948147595557</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
@@ -2560,16 +2560,16 @@
         <v>66</v>
       </c>
       <c r="C67" t="n">
-        <v>57.69599988222345</v>
+        <v>9.37559998086131</v>
       </c>
       <c r="D67" t="n">
-        <v>5.099019513592784</v>
+        <v>0.8285906709588275</v>
       </c>
       <c r="E67" t="n">
-        <v>21.98091342237604</v>
+        <v>3.571898431136106</v>
       </c>
       <c r="F67" t="n">
-        <v>21.38429629289573</v>
+        <v>3.474948147595557</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
@@ -2592,16 +2592,16 @@
         <v>67</v>
       </c>
       <c r="C68" t="n">
-        <v>29.32231542966223</v>
+        <v>4.764876257320112</v>
       </c>
       <c r="D68" t="n">
-        <v>11.29536697505089</v>
+        <v>1.835497133445769</v>
       </c>
       <c r="E68" t="n">
-        <v>21.98091342237604</v>
+        <v>3.571898431136106</v>
       </c>
       <c r="F68" t="n">
-        <v>21.38429629289573</v>
+        <v>3.474948147595557</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
@@ -2624,16 +2624,16 @@
         <v>68</v>
       </c>
       <c r="C69" t="n">
-        <v>54.93692154369754</v>
+        <v>8.92724975085085</v>
       </c>
       <c r="D69" t="n">
-        <v>37.85749469505379</v>
+        <v>6.151842887946242</v>
       </c>
       <c r="E69" t="n">
-        <v>21.98091342237604</v>
+        <v>3.571898431136106</v>
       </c>
       <c r="F69" t="n">
-        <v>21.38429629289573</v>
+        <v>3.474948147595557</v>
       </c>
       <c r="G69" t="inlineStr">
         <is>
@@ -2656,16 +2656,16 @@
         <v>69</v>
       </c>
       <c r="C70" t="n">
-        <v>40.93550711836063</v>
+        <v>6.652019906733602</v>
       </c>
       <c r="D70" t="n">
-        <v>21.18962010041709</v>
+        <v>3.443313266317777</v>
       </c>
       <c r="E70" t="n">
-        <v>21.98091342237604</v>
+        <v>3.571898431136106</v>
       </c>
       <c r="F70" t="n">
-        <v>21.38429629289573</v>
+        <v>3.474948147595557</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
@@ -2688,16 +2688,16 @@
         <v>70</v>
       </c>
       <c r="C71" t="n">
-        <v>38.42279773350198</v>
+        <v>6.243704631694072</v>
       </c>
       <c r="D71" t="n">
-        <v>16.54629867976521</v>
+        <v>2.688773535461846</v>
       </c>
       <c r="E71" t="n">
-        <v>21.98091342237604</v>
+        <v>3.571898431136106</v>
       </c>
       <c r="F71" t="n">
-        <v>21.38429629289573</v>
+        <v>3.474948147595557</v>
       </c>
       <c r="G71" t="inlineStr">
         <is>
@@ -2720,16 +2720,16 @@
         <v>71</v>
       </c>
       <c r="C72" t="n">
-        <v>77.24441616997679</v>
+        <v>12.55221762762123</v>
       </c>
       <c r="D72" t="n">
-        <v>18.02117777673886</v>
+        <v>2.928441388720065</v>
       </c>
       <c r="E72" t="n">
-        <v>21.98091342237604</v>
+        <v>3.571898431136106</v>
       </c>
       <c r="F72" t="n">
-        <v>21.38429629289573</v>
+        <v>3.474948147595557</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
@@ -2752,16 +2752,16 @@
         <v>72</v>
       </c>
       <c r="C73" t="n">
-        <v>46.83609174060719</v>
+        <v>7.610864907848669</v>
       </c>
       <c r="D73" t="n">
-        <v>14.59748427952888</v>
+        <v>2.372091195423444</v>
       </c>
       <c r="E73" t="n">
-        <v>21.98091342237604</v>
+        <v>3.571898431136106</v>
       </c>
       <c r="F73" t="n">
-        <v>21.38429629289573</v>
+        <v>3.474948147595557</v>
       </c>
       <c r="G73" t="inlineStr">
         <is>
@@ -2784,16 +2784,16 @@
         <v>73</v>
       </c>
       <c r="C74" t="n">
-        <v>47.64365867502458</v>
+        <v>7.742094534691494</v>
       </c>
       <c r="D74" t="n">
-        <v>26.41968962724581</v>
+        <v>4.293199564427445</v>
       </c>
       <c r="E74" t="n">
-        <v>21.98091342237604</v>
+        <v>3.571898431136106</v>
       </c>
       <c r="F74" t="n">
-        <v>21.38429629289573</v>
+        <v>3.474948147595557</v>
       </c>
       <c r="G74" t="inlineStr">
         <is>
@@ -2816,16 +2816,16 @@
         <v>74</v>
       </c>
       <c r="C75" t="n">
-        <v>45.99965000102264</v>
+        <v>7.47494312516618</v>
       </c>
       <c r="D75" t="n">
-        <v>14.71885003938049</v>
+        <v>2.39181313139933</v>
       </c>
       <c r="E75" t="n">
-        <v>21.98091342237604</v>
+        <v>3.571898431136106</v>
       </c>
       <c r="F75" t="n">
-        <v>21.38429629289573</v>
+        <v>3.474948147595557</v>
       </c>
       <c r="G75" t="inlineStr">
         <is>
@@ -2848,16 +2848,16 @@
         <v>75</v>
       </c>
       <c r="C76" t="n">
-        <v>46.58019817251606</v>
+        <v>7.56928220303386</v>
       </c>
       <c r="D76" t="n">
-        <v>23.98130507767843</v>
+        <v>3.896962075122745</v>
       </c>
       <c r="E76" t="n">
-        <v>21.98091342237604</v>
+        <v>3.571898431136106</v>
       </c>
       <c r="F76" t="n">
-        <v>21.38429629289573</v>
+        <v>3.474948147595557</v>
       </c>
       <c r="G76" t="inlineStr">
         <is>
@@ -2880,16 +2880,16 @@
         <v>76</v>
       </c>
       <c r="C77" t="n">
-        <v>64.72927560963538</v>
+        <v>10.51850728656575</v>
       </c>
       <c r="D77" t="n">
-        <v>39.51145171803648</v>
+        <v>6.420610904180927</v>
       </c>
       <c r="E77" t="n">
-        <v>21.98091342237604</v>
+        <v>3.571898431136106</v>
       </c>
       <c r="F77" t="n">
-        <v>21.38429629289573</v>
+        <v>3.474948147595557</v>
       </c>
       <c r="G77" t="inlineStr">
         <is>
@@ -2912,16 +2912,16 @@
         <v>77</v>
       </c>
       <c r="C78" t="n">
-        <v>81.14252058152569</v>
+        <v>13.18565959449792</v>
       </c>
       <c r="D78" t="n">
-        <v>22.33788797683041</v>
+        <v>3.629906796234942</v>
       </c>
       <c r="E78" t="n">
-        <v>21.98091342237604</v>
+        <v>3.571898431136106</v>
       </c>
       <c r="F78" t="n">
-        <v>21.38429629289573</v>
+        <v>3.474948147595557</v>
       </c>
       <c r="G78" t="inlineStr">
         <is>
@@ -2944,16 +2944,16 @@
         <v>78</v>
       </c>
       <c r="C79" t="n">
-        <v>59.95618469461917</v>
+        <v>9.742880012875615</v>
       </c>
       <c r="D79" t="n">
-        <v>13.88214506088327</v>
+        <v>2.255848572393531</v>
       </c>
       <c r="E79" t="n">
-        <v>21.98091342237604</v>
+        <v>3.571898431136106</v>
       </c>
       <c r="F79" t="n">
-        <v>21.38429629289573</v>
+        <v>3.474948147595557</v>
       </c>
       <c r="G79" t="inlineStr">
         <is>
@@ -2976,16 +2976,16 @@
         <v>79</v>
       </c>
       <c r="C80" t="n">
-        <v>62.33186440955483</v>
+        <v>10.12892796655266</v>
       </c>
       <c r="D80" t="n">
-        <v>34.24605902003059</v>
+        <v>5.56498459075497</v>
       </c>
       <c r="E80" t="n">
-        <v>21.98091342237604</v>
+        <v>3.571898431136106</v>
       </c>
       <c r="F80" t="n">
-        <v>21.38429629289573</v>
+        <v>3.474948147595557</v>
       </c>
       <c r="G80" t="inlineStr">
         <is>
@@ -3008,16 +3008,16 @@
         <v>80</v>
       </c>
       <c r="C81" t="n">
-        <v>40.2017725596947</v>
+        <v>6.53278804095039</v>
       </c>
       <c r="D81" t="n">
-        <v>10.67964094186879</v>
+        <v>1.735441653053679</v>
       </c>
       <c r="E81" t="n">
-        <v>21.98091342237604</v>
+        <v>3.571898431136106</v>
       </c>
       <c r="F81" t="n">
-        <v>21.38429629289573</v>
+        <v>3.474948147595557</v>
       </c>
       <c r="G81" t="inlineStr">
         <is>
@@ -3040,16 +3040,16 @@
         <v>81</v>
       </c>
       <c r="C82" t="n">
-        <v>75.69160019926969</v>
+        <v>12.29988503238132</v>
       </c>
       <c r="D82" t="n">
-        <v>50.46591049546761</v>
+        <v>8.200710455513487</v>
       </c>
       <c r="E82" t="n">
-        <v>21.98091342237604</v>
+        <v>3.571898431136106</v>
       </c>
       <c r="F82" t="n">
-        <v>21.38429629289573</v>
+        <v>3.474948147595557</v>
       </c>
       <c r="G82" t="inlineStr">
         <is>
@@ -3072,16 +3072,16 @@
         <v>82</v>
       </c>
       <c r="C83" t="n">
-        <v>60.34850854426224</v>
+        <v>9.806632638442615</v>
       </c>
       <c r="D83" t="n">
-        <v>34.29770494360094</v>
+        <v>5.573377053335153</v>
       </c>
       <c r="E83" t="n">
-        <v>21.98091342237604</v>
+        <v>3.571898431136106</v>
       </c>
       <c r="F83" t="n">
-        <v>21.38429629289573</v>
+        <v>3.474948147595557</v>
       </c>
       <c r="G83" t="inlineStr">
         <is>
@@ -3104,16 +3104,16 @@
         <v>83</v>
       </c>
       <c r="C84" t="n">
-        <v>60.24874292606007</v>
+        <v>9.790420725484763</v>
       </c>
       <c r="D84" t="n">
-        <v>28.16830895481991</v>
+        <v>4.577350205158235</v>
       </c>
       <c r="E84" t="n">
-        <v>21.98091342237604</v>
+        <v>3.571898431136106</v>
       </c>
       <c r="F84" t="n">
-        <v>21.38429629289573</v>
+        <v>3.474948147595557</v>
       </c>
       <c r="G84" t="inlineStr">
         <is>
@@ -3136,16 +3136,16 @@
         <v>84</v>
       </c>
       <c r="C85" t="n">
-        <v>68.36740708187419</v>
+        <v>11.10970365080456</v>
       </c>
       <c r="D85" t="n">
-        <v>36.08538231565142</v>
+        <v>5.863874626293355</v>
       </c>
       <c r="E85" t="n">
-        <v>21.98091342237604</v>
+        <v>3.571898431136106</v>
       </c>
       <c r="F85" t="n">
-        <v>21.38429629289573</v>
+        <v>3.474948147595557</v>
       </c>
       <c r="G85" t="inlineStr">
         <is>
@@ -3168,16 +3168,16 @@
         <v>85</v>
       </c>
       <c r="C86" t="n">
-        <v>65.26763287197259</v>
+        <v>10.60599034169555</v>
       </c>
       <c r="D86" t="n">
-        <v>35.8503835404867</v>
+        <v>5.825687325329089</v>
       </c>
       <c r="E86" t="n">
-        <v>21.98091342237604</v>
+        <v>3.571898431136106</v>
       </c>
       <c r="F86" t="n">
-        <v>21.38429629289573</v>
+        <v>3.474948147595557</v>
       </c>
       <c r="G86" t="inlineStr">
         <is>
@@ -3200,16 +3200,16 @@
         <v>86</v>
       </c>
       <c r="C87" t="n">
-        <v>67.41909517565688</v>
+        <v>10.95560296604424</v>
       </c>
       <c r="D87" t="n">
-        <v>36.13026519396366</v>
+        <v>5.871168094019095</v>
       </c>
       <c r="E87" t="n">
-        <v>21.98091342237604</v>
+        <v>3.571898431136106</v>
       </c>
       <c r="F87" t="n">
-        <v>21.38429629289573</v>
+        <v>3.474948147595557</v>
       </c>
       <c r="G87" t="inlineStr">
         <is>
@@ -3232,16 +3232,16 @@
         <v>87</v>
       </c>
       <c r="C88" t="n">
-        <v>69.66754393015557</v>
+        <v>11.32097588865028</v>
       </c>
       <c r="D88" t="n">
-        <v>41.33889424957781</v>
+        <v>6.717570315556395</v>
       </c>
       <c r="E88" t="n">
-        <v>21.98091342237604</v>
+        <v>3.571898431136106</v>
       </c>
       <c r="F88" t="n">
-        <v>21.38429629289573</v>
+        <v>3.474948147595557</v>
       </c>
       <c r="G88" t="inlineStr">
         <is>
@@ -3264,16 +3264,16 @@
         <v>88</v>
       </c>
       <c r="C89" t="n">
-        <v>94.97849726484175</v>
+        <v>15.43400580553678</v>
       </c>
       <c r="D89" t="n">
-        <v>68.85552624280363</v>
+        <v>11.18902301445559</v>
       </c>
       <c r="E89" t="n">
-        <v>21.98091342237604</v>
+        <v>3.571898431136106</v>
       </c>
       <c r="F89" t="n">
-        <v>21.38429629289573</v>
+        <v>3.474948147595557</v>
       </c>
       <c r="G89" t="inlineStr">
         <is>
@@ -3296,16 +3296,16 @@
         <v>89</v>
       </c>
       <c r="C90" t="n">
-        <v>77.77179873160539</v>
+        <v>12.63791729388588</v>
       </c>
       <c r="D90" t="n">
-        <v>41.90416615653196</v>
+        <v>6.809427000436443</v>
       </c>
       <c r="E90" t="n">
-        <v>21.98091342237604</v>
+        <v>3.571898431136106</v>
       </c>
       <c r="F90" t="n">
-        <v>21.38429629289573</v>
+        <v>3.474948147595557</v>
       </c>
       <c r="G90" t="inlineStr">
         <is>
@@ -3328,16 +3328,16 @@
         <v>90</v>
       </c>
       <c r="C91" t="n">
-        <v>81.5410851932001</v>
+        <v>13.25042634389502</v>
       </c>
       <c r="D91" t="n">
-        <v>50.2301413253883</v>
+        <v>8.1623979653756</v>
       </c>
       <c r="E91" t="n">
-        <v>21.98091342237604</v>
+        <v>3.571898431136106</v>
       </c>
       <c r="F91" t="n">
-        <v>21.38429629289573</v>
+        <v>3.474948147595557</v>
       </c>
       <c r="G91" t="inlineStr">
         <is>
@@ -3360,16 +3360,16 @@
         <v>91</v>
       </c>
       <c r="C92" t="n">
-        <v>107.369141552757</v>
+        <v>17.44748550232301</v>
       </c>
       <c r="D92" t="n">
-        <v>51.10772935672255</v>
+        <v>8.305006020467415</v>
       </c>
       <c r="E92" t="n">
-        <v>21.98091342237604</v>
+        <v>3.571898431136106</v>
       </c>
       <c r="F92" t="n">
-        <v>21.38429629289573</v>
+        <v>3.474948147595557</v>
       </c>
       <c r="G92" t="inlineStr">
         <is>
@@ -3392,16 +3392,16 @@
         <v>92</v>
       </c>
       <c r="C93" t="n">
-        <v>83.67526708510859</v>
+        <v>13.59723090133015</v>
       </c>
       <c r="D93" t="n">
-        <v>55.72640434734726</v>
+        <v>9.05554070644393</v>
       </c>
       <c r="E93" t="n">
-        <v>21.98091342237604</v>
+        <v>3.571898431136106</v>
       </c>
       <c r="F93" t="n">
-        <v>21.38429629289573</v>
+        <v>3.474948147595557</v>
       </c>
       <c r="G93" t="inlineStr">
         <is>
@@ -3424,16 +3424,16 @@
         <v>93</v>
       </c>
       <c r="C94" t="n">
-        <v>82.17369073966128</v>
+        <v>13.35322474519496</v>
       </c>
       <c r="D94" t="n">
-        <v>50.05996608213439</v>
+        <v>8.13474448834684</v>
       </c>
       <c r="E94" t="n">
-        <v>21.98091342237604</v>
+        <v>3.571898431136106</v>
       </c>
       <c r="F94" t="n">
-        <v>21.38429629289573</v>
+        <v>3.474948147595557</v>
       </c>
       <c r="G94" t="inlineStr">
         <is>
@@ -3456,16 +3456,16 @@
         <v>94</v>
       </c>
       <c r="C95" t="n">
-        <v>84.63318087091344</v>
+        <v>13.75289189152343</v>
       </c>
       <c r="D95" t="n">
-        <v>52.13587027099013</v>
+        <v>8.472078919035896</v>
       </c>
       <c r="E95" t="n">
-        <v>21.98091342237604</v>
+        <v>3.571898431136106</v>
       </c>
       <c r="F95" t="n">
-        <v>21.38429629289573</v>
+        <v>3.474948147595557</v>
       </c>
       <c r="G95" t="inlineStr">
         <is>
@@ -3488,16 +3488,16 @@
         <v>95</v>
       </c>
       <c r="C96" t="n">
-        <v>85.10582275944785</v>
+        <v>13.82969619841028</v>
       </c>
       <c r="D96" t="n">
-        <v>52.68920863010798</v>
+        <v>8.561996402392548</v>
       </c>
       <c r="E96" t="n">
-        <v>21.98091342237604</v>
+        <v>3.571898431136106</v>
       </c>
       <c r="F96" t="n">
-        <v>21.38429629289573</v>
+        <v>3.474948147595557</v>
       </c>
       <c r="G96" t="inlineStr">
         <is>
@@ -3520,16 +3520,16 @@
         <v>96</v>
       </c>
       <c r="C97" t="n">
-        <v>101.8097064324123</v>
+        <v>16.54407729526701</v>
       </c>
       <c r="D97" t="n">
-        <v>73.15520217099998</v>
+        <v>11.8877203527875</v>
       </c>
       <c r="E97" t="n">
-        <v>21.98091342237604</v>
+        <v>3.571898431136106</v>
       </c>
       <c r="F97" t="n">
-        <v>21.38429629289573</v>
+        <v>3.474948147595557</v>
       </c>
       <c r="G97" t="inlineStr">
         <is>
